--- a/main/ig/ValueSet-act-type-ror-valueset.xlsx
+++ b/main/ig/ValueSet-act-type-ror-valueset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-21T15:54:27+00:00</t>
+    <t>2026-01-30T10:12:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-act-type-ror-valueset.xlsx
+++ b/main/ig/ValueSet-act-type-ror-valueset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T10:12:59+00:00</t>
+    <t>2026-03-09T13:22:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-act-type-ror-valueset.xlsx
+++ b/main/ig/ValueSet-act-type-ror-valueset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-09T13:22:43+00:00</t>
+    <t>2026-03-17T11:12:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-act-type-ror-valueset.xlsx
+++ b/main/ig/ValueSet-act-type-ror-valueset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-17T11:12:47+00:00</t>
+    <t>2026-03-23T15:20:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-act-type-ror-valueset.xlsx
+++ b/main/ig/ValueSet-act-type-ror-valueset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-23T15:20:38+00:00</t>
+    <t>2026-03-24T09:51:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-act-type-ror-valueset.xlsx
+++ b/main/ig/ValueSet-act-type-ror-valueset.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0-snapshot-1</t>
+    <t>0.7.0-snapshot-2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T09:51:35+00:00</t>
+    <t>2026-03-24T10:30:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-act-type-ror-valueset.xlsx
+++ b/main/ig/ValueSet-act-type-ror-valueset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T08:33:49+00:00</t>
+    <t>2026-04-29T13:16:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-act-type-ror-valueset.xlsx
+++ b/main/ig/ValueSet-act-type-ror-valueset.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0-snapshot-2</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T13:16:27+00:00</t>
+    <t>2026-04-29T15:21:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-act-type-ror-valueset.xlsx
+++ b/main/ig/ValueSet-act-type-ror-valueset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T15:21:13+00:00</t>
+    <t>2026-04-29T15:21:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-act-type-ror-valueset.xlsx
+++ b/main/ig/ValueSet-act-type-ror-valueset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T15:21:33+00:00</t>
+    <t>2026-07-23T07:54:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-act-type-ror-valueset.xlsx
+++ b/main/ig/ValueSet-act-type-ror-valueset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T07:54:45+00:00</t>
+    <t>2026-07-23T08:00:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-act-type-ror-valueset.xlsx
+++ b/main/ig/ValueSet-act-type-ror-valueset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T08:00:07+00:00</t>
+    <t>2026-07-23T08:13:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
